--- a/stories/arbres/TREE-JEU-029.xlsx
+++ b/stories/arbres/TREE-JEU-029.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Titouan joue dans le jardin avec papa. Parfois l'autre gagne. Papa dit : on peut être déçu. C'est permis. On peut rejouer plus tard. L'autre peut gagner.</t>
+          <t>Titouan joue dans le jardin avec papa. Parfois l'autre gagne. On peut être déçu. C'est permis. On peut rejouer plus tard. L'autre peut gagner.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan joue dans le jardin avec papa. Parfois l'autre gagne.
+papa|On peut être déçu. C'est permis. On peut rejouer plus tard. L'autre peut gagner.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, la course, ou le ballon.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1677,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Aux cubes, l'autre peut gagner. Titouan est déçu. C'est permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Aux cubes, l'autre gagne. Que fait Titouan ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2185,6 +2228,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sara.</t>
         </is>
       </c>
     </row>
@@ -2349,6 +2397,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|L'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2535,6 +2588,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre bravo, une pause, ou plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2697,6 +2755,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit bravo. Léa a gagné à les cubes. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2922,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3089,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit une pause. Léa a gagné à les cubes. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3256,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3423,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit plus tard. Léa a gagné à les cubes. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3590,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3757,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|L'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3948,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre bravo, une pause, ou plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4017,6 +4115,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit bravo. Tom a gagné à les cubes. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4282,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4449,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit une pause. Tom a gagné à les cubes. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4616,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4783,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit plus tard. Tom a gagné à les cubes. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4950,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5117,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|L'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5175,6 +5308,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre bravo, une pause, ou plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5337,6 +5475,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit bravo. Sara a gagné à les cubes. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5499,6 +5642,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5661,6 +5809,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit une pause. Sara a gagné à les cubes. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5823,6 +5976,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5985,6 +6143,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit plus tard. Sara a gagné à les cubes. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6147,6 +6310,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6309,6 +6477,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|À la course, l'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6662,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|À la course, l'autre gagne. Que fait Titouan ?</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6835,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Déçu permis. Rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6845,6 +7028,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sara.</t>
         </is>
       </c>
     </row>
@@ -7009,6 +7197,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|L'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7195,6 +7388,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre bravo, une pause, ou plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7357,6 +7555,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit bravo. Léa a gagné à la course. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7722,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7889,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit une pause. Léa a gagné à la course. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8056,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8223,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit plus tard. Léa a gagné à la course. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8390,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8557,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|L'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8515,6 +8748,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre bravo, une pause, ou plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8677,6 +8915,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit bravo. Tom a gagné à la course. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8839,6 +9082,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9001,6 +9249,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit une pause. Tom a gagné à la course. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9163,6 +9416,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9325,6 +9583,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit plus tard. Tom a gagné à la course. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9487,6 +9750,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9649,6 +9917,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|L'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9835,6 +10108,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre bravo, une pause, ou plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9997,6 +10275,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit bravo. Sara a gagné à la course. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10159,6 +10442,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10321,6 +10609,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit une pause. Sara a gagné à la course. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10483,6 +10776,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10645,6 +10943,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit plus tard. Sara a gagné à la course. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10807,6 +11110,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10969,6 +11277,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Au ballon, l'autre peut gagner. Titouan est déçu. Permis. On peut rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11149,6 +11462,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Au ballon, l'autre gagne. Que fait Titouan ?</t>
         </is>
       </c>
     </row>
@@ -11317,6 +11635,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan a dit bravo. Il pourra rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11505,6 +11828,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sara.</t>
         </is>
       </c>
     </row>
@@ -11669,6 +11997,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|L'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11855,6 +12188,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre bravo, une pause, ou plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12017,6 +12355,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit bravo. Léa a gagné à le ballon. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12179,6 +12522,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12341,6 +12689,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit une pause. Léa a gagné à le ballon. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12503,6 +12856,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12665,6 +13023,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit plus tard. Léa a gagné à le ballon. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12827,6 +13190,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12989,6 +13357,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|L'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13175,6 +13548,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre bravo, une pause, ou plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13337,6 +13715,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit bravo. Tom a gagné à le ballon. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13499,6 +13882,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13661,6 +14049,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit une pause. Tom a gagné à le ballon. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13823,6 +14216,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13985,6 +14383,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit plus tard. Tom a gagné à le ballon. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14147,6 +14550,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14309,6 +14717,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|L'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14495,6 +14908,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre bravo, une pause, ou plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14657,6 +15075,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit bravo. Sara a gagné à le ballon. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14819,6 +15242,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14981,6 +15409,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit une pause. Sara a gagné à le ballon. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15143,6 +15576,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15305,6 +15743,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Titouan choisit plus tard. Sara a gagné à le ballon. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15467,6 +15910,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15485,7 +15933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15516,6 +15964,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-JEU-029.xlsx
+++ b/stories/arbres/TREE-JEU-029.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 papa|On peut être déçu. C'est permis. On peut rejouer plus tard. L'autre peut gagner.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1515,6 +1521,7 @@
           <t>narrateur|On peut prendre les cubes, la course, ou le ballon.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
           <t>narrateur|Aux cubes, l'autre peut gagner. Titouan est déçu. C'est permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Aux cubes, l'autre gagne. Que fait Titouan ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2235,6 +2245,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sara.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2402,6 +2413,7 @@
           <t>narrateur|L'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2605,7 @@
           <t>narrateur|On peut prendre bravo, une pause, ou plus tard.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2760,6 +2773,7 @@
           <t>narrateur|Titouan choisit bravo. Léa a gagné à les cubes. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2927,6 +2941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3109,7 @@
           <t>narrateur|Titouan choisit une pause. Léa a gagné à les cubes. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3445,7 @@
           <t>narrateur|Titouan choisit plus tard. Léa a gagné à les cubes. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3762,6 +3781,7 @@
           <t>narrateur|L'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3953,6 +3973,7 @@
           <t>narrateur|On peut prendre bravo, une pause, ou plus tard.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4120,6 +4141,7 @@
           <t>narrateur|Titouan choisit bravo. Tom a gagné à les cubes. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4287,6 +4309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4454,6 +4477,7 @@
           <t>narrateur|Titouan choisit une pause. Tom a gagné à les cubes. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4621,6 +4645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4788,6 +4813,7 @@
           <t>narrateur|Titouan choisit plus tard. Tom a gagné à les cubes. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4955,6 +4981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5122,6 +5149,7 @@
           <t>narrateur|L'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5313,6 +5341,7 @@
           <t>narrateur|On peut prendre bravo, une pause, ou plus tard.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5480,6 +5509,7 @@
           <t>narrateur|Titouan choisit bravo. Sara a gagné à les cubes. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5647,6 +5677,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5814,6 +5845,7 @@
           <t>narrateur|Titouan choisit une pause. Sara a gagné à les cubes. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5981,6 +6013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6148,6 +6181,7 @@
           <t>narrateur|Titouan choisit plus tard. Sara a gagné à les cubes. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6315,6 +6349,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6482,6 +6517,7 @@
           <t>narrateur|À la course, l'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6669,6 +6705,7 @@
           <t>narrateur|À la course, l'autre gagne. Que fait Titouan ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6840,6 +6877,7 @@
           <t>narrateur|Oui. Déçu permis. Rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7035,6 +7073,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sara.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7202,6 +7241,7 @@
           <t>narrateur|L'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7393,6 +7433,7 @@
           <t>narrateur|On peut prendre bravo, une pause, ou plus tard.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7560,6 +7601,7 @@
           <t>narrateur|Titouan choisit bravo. Léa a gagné à la course. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7727,6 +7769,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7894,6 +7937,7 @@
           <t>narrateur|Titouan choisit une pause. Léa a gagné à la course. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8061,6 +8105,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8228,6 +8273,7 @@
           <t>narrateur|Titouan choisit plus tard. Léa a gagné à la course. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8395,6 +8441,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8562,6 +8609,7 @@
           <t>narrateur|L'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8753,6 +8801,7 @@
           <t>narrateur|On peut prendre bravo, une pause, ou plus tard.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8920,6 +8969,7 @@
           <t>narrateur|Titouan choisit bravo. Tom a gagné à la course. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9087,6 +9137,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9254,6 +9305,7 @@
           <t>narrateur|Titouan choisit une pause. Tom a gagné à la course. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9421,6 +9473,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9588,6 +9641,7 @@
           <t>narrateur|Titouan choisit plus tard. Tom a gagné à la course. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9755,6 +9809,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9922,6 +9977,7 @@
           <t>narrateur|L'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10113,6 +10169,7 @@
           <t>narrateur|On peut prendre bravo, une pause, ou plus tard.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10280,6 +10337,7 @@
           <t>narrateur|Titouan choisit bravo. Sara a gagné à la course. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10447,6 +10505,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10614,6 +10673,7 @@
           <t>narrateur|Titouan choisit une pause. Sara a gagné à la course. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10781,6 +10841,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10948,6 +11009,7 @@
           <t>narrateur|Titouan choisit plus tard. Sara a gagné à la course. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11115,6 +11177,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11282,6 +11345,7 @@
           <t>narrateur|Au ballon, l'autre peut gagner. Titouan est déçu. Permis. On peut rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11469,6 +11533,7 @@
           <t>narrateur|Au ballon, l'autre gagne. Que fait Titouan ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11640,6 +11705,7 @@
           <t>narrateur|Titouan a dit bravo. Il pourra rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11835,6 +11901,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sara.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12002,6 +12069,7 @@
           <t>narrateur|L'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12193,6 +12261,7 @@
           <t>narrateur|On peut prendre bravo, une pause, ou plus tard.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12360,6 +12429,7 @@
           <t>narrateur|Titouan choisit bravo. Léa a gagné à le ballon. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12527,6 +12597,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12694,6 +12765,7 @@
           <t>narrateur|Titouan choisit une pause. Léa a gagné à le ballon. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12861,6 +12933,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13028,6 +13101,7 @@
           <t>narrateur|Titouan choisit plus tard. Léa a gagné à le ballon. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13195,6 +13269,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13362,6 +13437,7 @@
           <t>narrateur|L'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13553,6 +13629,7 @@
           <t>narrateur|On peut prendre bravo, une pause, ou plus tard.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13720,6 +13797,7 @@
           <t>narrateur|Titouan choisit bravo. Tom a gagné à le ballon. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13887,6 +13965,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14054,6 +14133,7 @@
           <t>narrateur|Titouan choisit une pause. Tom a gagné à le ballon. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14221,6 +14301,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14388,6 +14469,7 @@
           <t>narrateur|Titouan choisit plus tard. Tom a gagné à le ballon. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14555,6 +14637,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14722,6 +14805,7 @@
           <t>narrateur|L'autre peut gagner. Titouan est déçu. Permis. Rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14913,6 +14997,7 @@
           <t>narrateur|On peut prendre bravo, une pause, ou plus tard.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15080,6 +15165,7 @@
           <t>narrateur|Titouan choisit bravo. Sara a gagné à le ballon. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15247,6 +15333,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15414,6 +15501,7 @@
           <t>narrateur|Titouan choisit une pause. Sara a gagné à le ballon. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15581,6 +15669,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15748,6 +15837,7 @@
           <t>narrateur|Titouan choisit plus tard. Sara a gagné à le ballon. L'autre peut gagner. Déçu permis. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15915,6 +16005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15933,7 +16024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15971,6 +16062,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15985,7 +16090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16172,6 +16277,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
